--- a/hypermesh/仿真建模规范-手机.xlsx
+++ b/hypermesh/仿真建模规范-手机.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480" activeTab="3"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="1-主板建模规范" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="450">
   <si>
     <t>主板建模规范</t>
   </si>
@@ -70,7 +70,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>PCB_MAIN</t>
+    <t>MB_PCB</t>
   </si>
   <si>
     <t>主板PCB</t>
@@ -82,7 +82,7 @@
     <t>pcb_161</t>
   </si>
   <si>
-    <t>PCB_MAIN_SHIELD</t>
+    <t>MBC_SHIELD</t>
   </si>
   <si>
     <t>主板屏蔽罩</t>
@@ -91,7 +91,7 @@
     <t>cu_c7521_for_shield</t>
   </si>
   <si>
-    <t>PCB_MAIN_SHIELD_CU</t>
+    <t>MBC_SHIELD_CU</t>
   </si>
   <si>
     <t>主板屏蔽罩铜箔</t>
@@ -100,7 +100,7 @@
     <t>C3D8R</t>
   </si>
   <si>
-    <t>PCB_MAIN_BTB</t>
+    <t>MBC_BTB</t>
   </si>
   <si>
     <t>主板板对板连接器</t>
@@ -109,7 +109,7 @@
     <t>pc+10%gf</t>
   </si>
   <si>
-    <t>PCB_MAIN_BTB_RUBBER</t>
+    <t>MBC_BTB_RUBBER</t>
   </si>
   <si>
     <t>主板连接器胶垫</t>
@@ -118,7 +118,7 @@
     <t>rubber</t>
   </si>
   <si>
-    <t>PCB_MAIN_REC_STEEL</t>
+    <t>MBC_REC_STEEL</t>
   </si>
   <si>
     <t>主板听筒钢片</t>
@@ -130,7 +130,7 @@
     <t>sus301_075h</t>
   </si>
   <si>
-    <t>PCB_MAIN_BOSS_STEEL</t>
+    <t>MBC_BOSS_STEEL</t>
   </si>
   <si>
     <t>主板支撑钢片</t>
@@ -151,13 +151,13 @@
     <t>pc_EXL1414</t>
   </si>
   <si>
-    <t>PCB_MAIN_SPRING</t>
+    <t>MBC_SPRING</t>
   </si>
   <si>
     <t>主板弹片</t>
   </si>
   <si>
-    <t>PCB_MAIN_SHIELD_SOLDER</t>
+    <t>MBC_SHIELD_SOLDER</t>
   </si>
   <si>
     <t>屏蔽罩焊锡</t>
@@ -172,19 +172,19 @@
     <t>主板传感器及芯片部件</t>
   </si>
   <si>
-    <t>P_SENSOR_DIANCAOBAN</t>
-  </si>
-  <si>
-    <t>压力传感器DIANCAOBAN</t>
+    <t>P_SENSOR_DIANGAOAOBAN</t>
+  </si>
+  <si>
+    <t>压力传感器垫高板</t>
   </si>
   <si>
     <t>/</t>
   </si>
   <si>
-    <t>P_SENSOR_DIANCAOBAN_S OLDER</t>
-  </si>
-  <si>
-    <t>压力传感器DIANCAOBANS OLDER</t>
+    <t>P_SENSOR_DIANGAOAOBAN_SOLDER</t>
+  </si>
+  <si>
+    <t>压力传感器垫高板焊锡</t>
   </si>
   <si>
     <t>P_SENSOR_SOLDER</t>
@@ -199,7 +199,7 @@
     <t>压力传感器</t>
   </si>
   <si>
-    <t>PCB_MAIN_CSP_XXX</t>
+    <t>MBC_CSP_XXX</t>
   </si>
   <si>
     <t>主板CSP</t>
@@ -208,7 +208,7 @@
     <t>chip_package(树脂封装)</t>
   </si>
   <si>
-    <t>PCB_MAIN_BGA_XXX</t>
+    <t>MBC_BGA_XXX</t>
   </si>
   <si>
     <t>主板BGA</t>
@@ -220,22 +220,22 @@
     <t>(XXX代表芯片名称)</t>
   </si>
   <si>
-    <t>PCB_MAIN_CHIP_SOLDER</t>
-  </si>
-  <si>
-    <t>主板CHIP焊锡</t>
-  </si>
-  <si>
-    <t>参考下图，要求全六面体</t>
+    <t>MBC_CHIP_SOLDER</t>
+  </si>
+  <si>
+    <t>主板芯片焊锡</t>
+  </si>
+  <si>
+    <t>要求全六面体</t>
   </si>
   <si>
     <t>高度0.15，三层</t>
   </si>
   <si>
-    <t>PCB_MAIN_CHIP_UNDERFILL</t>
-  </si>
-  <si>
-    <t>主板CHIPUNDERFILL</t>
+    <t>MBC_CHIP_UNDERFILL</t>
+  </si>
+  <si>
+    <t>主板芯片底填胶</t>
   </si>
   <si>
     <t>underfill_for_chips</t>
@@ -247,7 +247,7 @@
     <t>要求和焊球共节点</t>
   </si>
   <si>
-    <t>PCB_MAIN_COMP_L</t>
+    <t>MBC_L</t>
   </si>
   <si>
     <t>主板元器件电感</t>
@@ -259,7 +259,7 @@
     <t>主板电感</t>
   </si>
   <si>
-    <t>PCB_MAIN_COMP_R</t>
+    <t>MBC_R</t>
   </si>
   <si>
     <t>主板元器件电阻</t>
@@ -268,7 +268,7 @@
     <t>主板电阻</t>
   </si>
   <si>
-    <t>PCB_MAIN_COMP_C0201</t>
+    <t>MBC_C0201</t>
   </si>
   <si>
     <t>主板元器件0201电容</t>
@@ -277,7 +277,7 @@
     <t>主板0201电容</t>
   </si>
   <si>
-    <t>PCB_MAIN_COMP_C0402</t>
+    <t>MBC_C0402</t>
   </si>
   <si>
     <t>主板元器件0402电容</t>
@@ -286,7 +286,7 @@
     <t>主板0402电容</t>
   </si>
   <si>
-    <t>PCB_MAIN_COMP_C0603</t>
+    <t>MBC_C0603</t>
   </si>
   <si>
     <t>主板元器件0603电容</t>
@@ -295,7 +295,7 @@
     <t>主板0603电容</t>
   </si>
   <si>
-    <t>PCB_MAIN_COMP</t>
+    <t>MBC_COMP</t>
   </si>
   <si>
     <t>主板元器件</t>
@@ -304,7 +304,7 @@
     <t>主板上其他器件</t>
   </si>
   <si>
-    <t>PCB_MAIN_CSP_XXX_COAT</t>
+    <t>MBC_CSP_XXX_COAT</t>
   </si>
   <si>
     <t>主板CSP_COAT</t>
@@ -322,82 +322,79 @@
     <t>小板建模规范</t>
   </si>
   <si>
-    <t>PCB_SUB</t>
-  </si>
-  <si>
     <t>小板PCB</t>
   </si>
   <si>
     <t>PBC_161</t>
   </si>
   <si>
-    <t>PCB_SUB_COMP_R</t>
+    <t>SBC_R</t>
   </si>
   <si>
     <t>小板元器件电阻</t>
   </si>
   <si>
-    <t>PCB_SUB_COMP_C0201</t>
+    <t>SBC_C0201</t>
   </si>
   <si>
     <t>小板元器件0201电容</t>
   </si>
   <si>
-    <t>PCB_SUB_COMP_C0402</t>
+    <t>SBC_C0402</t>
   </si>
   <si>
     <t>小板元器件0402电容</t>
   </si>
   <si>
-    <t>PCB_SUB_COMP_C0603</t>
+    <t>SBC_C0603</t>
   </si>
   <si>
     <t>小板元器件0603电容</t>
   </si>
   <si>
-    <t>PCB_SUB_COMP_L</t>
+    <t>SBC_L</t>
   </si>
   <si>
     <t>小板元器件电感</t>
   </si>
   <si>
-    <t>PCB_SUB_COMP_B</t>
+    <t>SBC_B</t>
   </si>
   <si>
     <t>小板元器件整流桥</t>
   </si>
   <si>
-    <t>PCB_SUB_COMP</t>
+    <t>SBC_COMP</t>
   </si>
   <si>
     <t>小板元器件</t>
   </si>
   <si>
-    <t>PCB_SUB_GLUE</t>
+    <t>SBC_GLUE</t>
   </si>
   <si>
     <t>小板器件点胶</t>
   </si>
   <si>
-    <t>PCB_SUB_MIC</t>
+    <t>SBC_MIC</t>
   </si>
   <si>
     <t>小板麦克风</t>
   </si>
   <si>
-    <t>PCB_SUB_MIC_SHIELDID</t>
+    <t>SBC_MIC_SHIELDID</t>
   </si>
   <si>
     <t>小板麦克风屏蔽罩</t>
   </si>
   <si>
-    <t>PCB_SUB_BTB</t>
+    <t>SBC_BTB</t>
   </si>
   <si>
     <t>小板板对板连接器</t>
   </si>
   <si>
-    <t>PCB_SUB_BTB_RUBBER</t>
+    <t>SBC_BTB_RUBBER</t>
   </si>
   <si>
     <t>小板板对板连接器胶圈</t>
@@ -406,7 +403,7 @@
     <t>rubber_90</t>
   </si>
   <si>
-    <t>PCB_SUB_SPRING</t>
+    <t>SBC_SPRING</t>
   </si>
   <si>
     <t>小板弹片</t>
@@ -484,19 +481,19 @@
     <t>摄像头建模规范</t>
   </si>
   <si>
-    <t>RFC_8M_LENS</t>
+    <t>RFC_XX_LENS</t>
   </si>
   <si>
     <t>后摄镜头</t>
   </si>
   <si>
-    <t>RFC_8M_IR_HOLDER</t>
+    <t>RFC_XX_IR_HOLDER</t>
   </si>
   <si>
     <t>后摄红外滤光片支架</t>
   </si>
   <si>
-    <t>RFC_8M_HOLDER_GLUE</t>
+    <t>RFC_XX_HOLDER_GLUE</t>
   </si>
   <si>
     <t>后摄支架点胶</t>
@@ -505,7 +502,7 @@
     <t>TP_glue_LDA</t>
   </si>
   <si>
-    <t>RFC_8M_PCB</t>
+    <t>RFC_XX_PCB</t>
   </si>
   <si>
     <t>后摄电路板</t>
@@ -514,7 +511,7 @@
     <t>PCB_242</t>
   </si>
   <si>
-    <t>RFC_8M_FPC</t>
+    <t>RFC_XX_FPC</t>
   </si>
   <si>
     <t>后摄柔性电路板</t>
@@ -523,7 +520,7 @@
     <t>FPC</t>
   </si>
   <si>
-    <t>RFC_8M_IR</t>
+    <t>RFC_XX_IR</t>
   </si>
   <si>
     <t>后摄红外滤光片</t>
@@ -532,7 +529,7 @@
     <t>lcd_glass</t>
   </si>
   <si>
-    <t>RFC_8M_IR_GLUE</t>
+    <t>RFC_XX_IR_GLUE</t>
   </si>
   <si>
     <t>后摄红外滤光片胶</t>
@@ -541,7 +538,7 @@
     <t>glue</t>
   </si>
   <si>
-    <t>RFC_8M_IC</t>
+    <t>RFC_XX_IC</t>
   </si>
   <si>
     <t>后摄芯片</t>
@@ -550,7 +547,7 @@
     <t>lcd_ic</t>
   </si>
   <si>
-    <t>RFC_8M_IC_GLUE</t>
+    <t>RFC_XX_IC_GLUE</t>
   </si>
   <si>
     <t>后摄芯片胶</t>
@@ -580,8 +577,30 @@
     <t>前壳屏幕胶</t>
   </si>
   <si>
-    <t>点胶：TP_glue_LDA
-泡棉胶：glue</t>
+    <r>
+      <t>点胶：TP_glue_LDA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4A5568"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF4A5568"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>泡棉胶：glue</t>
+    </r>
   </si>
   <si>
     <t>A_REC_DECO</t>
@@ -599,15 +618,39 @@
     <t>前壳听筒装饰件背胶</t>
   </si>
   <si>
+    <t>A_FFC_RUBBER</t>
+  </si>
+  <si>
+    <t>前摄胶套</t>
+  </si>
+  <si>
+    <t>rubber_75</t>
+  </si>
+  <si>
+    <t>A_FFC_BRACKET</t>
+  </si>
+  <si>
+    <t>前摄支架</t>
+  </si>
+  <si>
+    <t>pc+20%gf(具体参考工艺清单)</t>
+  </si>
+  <si>
+    <t>A_FFC_FOAM</t>
+  </si>
+  <si>
+    <t>前摄泡棉</t>
+  </si>
+  <si>
+    <t>foam</t>
+  </si>
+  <si>
     <t>A_LCM_ELEC_FOAM</t>
   </si>
   <si>
     <t>前壳显示模组导电泡棉</t>
   </si>
   <si>
-    <t>foam</t>
-  </si>
-  <si>
     <t>A_FOAM</t>
   </si>
   <si>
@@ -629,9 +672,6 @@
     <t>前壳橡胶</t>
   </si>
   <si>
-    <t>rubber_75</t>
-  </si>
-  <si>
     <t>A_MIC_RUBBER</t>
   </si>
   <si>
@@ -686,6 +726,39 @@
     <t>前壳电池泡棉</t>
   </si>
   <si>
+    <t>A_MIC_MESH</t>
+  </si>
+  <si>
+    <t>MIC防尘网</t>
+  </si>
+  <si>
+    <t>fabric_cloth</t>
+  </si>
+  <si>
+    <t>A_MIC_ADH</t>
+  </si>
+  <si>
+    <t>MIC背胶</t>
+  </si>
+  <si>
+    <t>A_MIC_FOAM</t>
+  </si>
+  <si>
+    <t>MIC密封泡棉</t>
+  </si>
+  <si>
+    <t>MIC密封胶套</t>
+  </si>
+  <si>
+    <t>A_WATER_LABEL</t>
+  </si>
+  <si>
+    <t>防水标签</t>
+  </si>
+  <si>
+    <t>pet</t>
+  </si>
+  <si>
     <t>前壳按键及连接器部件</t>
   </si>
   <si>
@@ -707,25 +780,22 @@
     <t>前壳听筒PET膜</t>
   </si>
   <si>
-    <t>pet</t>
-  </si>
-  <si>
     <t>POWERKEY_FPC</t>
   </si>
   <si>
-    <t>电源键柔性电路板</t>
+    <t>电源键FPC</t>
   </si>
   <si>
     <t>POWERKEY_FPC_GLUE</t>
   </si>
   <si>
-    <t>电源键柔性电路板胶</t>
+    <t>电源键FPC背胶</t>
   </si>
   <si>
     <t>POWERKEY_FPC_SUS</t>
   </si>
   <si>
-    <t>电源键柔性电路板钢片</t>
+    <t>电源键FPC补强钢片</t>
   </si>
   <si>
     <t>sus304_075h</t>
@@ -740,19 +810,19 @@
     <t>VOLKEY_FPC</t>
   </si>
   <si>
-    <t>音量键柔性电路板</t>
+    <t>音量键FPC</t>
   </si>
   <si>
     <t>VOLKEY_FPC_ADH</t>
   </si>
   <si>
-    <t>音量键柔性电路板背胶</t>
+    <t>音量键FPC背胶</t>
   </si>
   <si>
     <t>VOLKEY_FPC_SUS</t>
   </si>
   <si>
-    <t>音量键柔性电路板不锈钢片</t>
+    <t>音量键FPC补强钢片</t>
   </si>
   <si>
     <t>VOLKEY_DOME</t>
@@ -782,12 +852,6 @@
     <t>后壳组件建模规范（后壳组件全部B开头）</t>
   </si>
   <si>
-    <t>B_FFC_FOAM</t>
-  </si>
-  <si>
-    <t>后壳前摄泡棉</t>
-  </si>
-  <si>
     <t>B_NFC</t>
   </si>
   <si>
@@ -800,13 +864,16 @@
     <t>后壳盖板石墨片</t>
   </si>
   <si>
-    <t>B_COVER</t>
-  </si>
-  <si>
-    <t>后壳盖板</t>
-  </si>
-  <si>
-    <t>pc+20%gf(具体参考工艺清单)</t>
+    <t>B_COVER_PLASTIC</t>
+  </si>
+  <si>
+    <t>后壳盖板/主板支架</t>
+  </si>
+  <si>
+    <t>B_COVER_METAL</t>
+  </si>
+  <si>
+    <t>主板支架内嵌钢片</t>
   </si>
   <si>
     <t>B_RFC_FOAM</t>
@@ -815,6 +882,21 @@
     <t>后壳后摄泡棉</t>
   </si>
   <si>
+    <t>B_FLASH_LENS</t>
+  </si>
+  <si>
+    <t>闪光灯罩</t>
+  </si>
+  <si>
+    <t>pmma_mr200</t>
+  </si>
+  <si>
+    <t>B_FLASH_LENS_GLUE</t>
+  </si>
+  <si>
+    <t>闪光灯罩背胶</t>
+  </si>
+  <si>
     <t>BATT_COVER</t>
   </si>
   <si>
@@ -824,51 +906,84 @@
     <t>pc_EXL1414(具体参考工艺清单)</t>
   </si>
   <si>
+    <t>BATT_COVER_DECO</t>
+  </si>
+  <si>
+    <t>电池盖装饰件</t>
+  </si>
+  <si>
+    <t>0.5/0.8</t>
+  </si>
+  <si>
+    <t>BATT_COVER_DECO_ADH</t>
+  </si>
+  <si>
+    <t>电池盖装饰件背胶</t>
+  </si>
+  <si>
     <t>BATT_COVER_DECO_LENS</t>
   </si>
   <si>
-    <t>电池盖板装饰件镜片</t>
+    <t>电池盖装饰件镜片</t>
   </si>
   <si>
     <t>tp_corning_glass</t>
   </si>
   <si>
-    <t>BATT_COVER_DECO_LENS_GLUE</t>
-  </si>
-  <si>
-    <t>电池盖板装饰件镜片胶</t>
-  </si>
-  <si>
-    <t>B_FLASH_LENS</t>
-  </si>
-  <si>
-    <t>后壳闪光灯镜片</t>
-  </si>
-  <si>
-    <t>pmma_mr200</t>
-  </si>
-  <si>
-    <t>B_FLASH_LENS_GLUE</t>
-  </si>
-  <si>
-    <t>后壳闪光灯镜片胶</t>
+    <t>BATT_COVER_DECO_LENS_ADH</t>
+  </si>
+  <si>
+    <t>电池盖装饰件镜片胶</t>
+  </si>
+  <si>
+    <t>BATT_COVER_ADH</t>
+  </si>
+  <si>
+    <t>电池盖密封泡棉</t>
+  </si>
+  <si>
+    <t>BATT_FOAM</t>
+  </si>
+  <si>
+    <t>电池压紧泡棉</t>
+  </si>
+  <si>
+    <t>BATT_COVER_CODE</t>
+  </si>
+  <si>
+    <t>电池盖二维码</t>
   </si>
   <si>
     <t>后壳扬声器及卡托部件</t>
   </si>
   <si>
-    <t>SPK_BOX_COVER</t>
+    <t>SPK_BOX_COVER_PALSTIC</t>
   </si>
   <si>
     <t>扬声器音腔盖板</t>
   </si>
   <si>
+    <t>SPK_BOX_COVER_METAL</t>
+  </si>
+  <si>
+    <t>扬声器音腔钢片</t>
+  </si>
+  <si>
+    <t>sus304_05h(具体参考工艺清单)</t>
+  </si>
+  <si>
     <t>SPK</t>
   </si>
   <si>
     <t>扬声器</t>
   </si>
   <si>
+    <t>SPK_FPC</t>
+  </si>
+  <si>
+    <t>扬声器FPC</t>
+  </si>
+  <si>
     <t>SPK_GLUE</t>
   </si>
   <si>
@@ -887,7 +1002,13 @@
     <t>扬声器音腔泡棉</t>
   </si>
   <si>
-    <t>SIM_TRAY_PL</t>
+    <t>SPK_BOX_GRAPHITE</t>
+  </si>
+  <si>
+    <t>扬声器石墨片</t>
+  </si>
+  <si>
+    <t>SIM_TRAY_PALSTIC</t>
   </si>
   <si>
     <t>SIM卡托塑胶</t>
@@ -899,7 +1020,13 @@
     <t>SIM卡托钢片</t>
   </si>
   <si>
-    <t>sus304_05h(具体参考工艺清单)</t>
+    <t>SIM_TRAY_RUBBER</t>
+  </si>
+  <si>
+    <t>SIM卡托防水胶圈</t>
+  </si>
+  <si>
+    <t>rubber_55(具体参考工艺清单)</t>
   </si>
   <si>
     <t>VOLUME_RUBBER</t>
@@ -915,6 +1042,39 @@
   </si>
   <si>
     <t>音量键按键</t>
+  </si>
+  <si>
+    <t>SUB_FRAME_PLASTIC</t>
+  </si>
+  <si>
+    <t>小板支架塑胶</t>
+  </si>
+  <si>
+    <t>SUB_FRAME_STEEL</t>
+  </si>
+  <si>
+    <t>小板支架钢片</t>
+  </si>
+  <si>
+    <t>EARJACK_RUBBER</t>
+  </si>
+  <si>
+    <t>耳机胶套</t>
+  </si>
+  <si>
+    <t>USB_RUBBER</t>
+  </si>
+  <si>
+    <t>USB胶套</t>
+  </si>
+  <si>
+    <t>SPK_magnet</t>
+  </si>
+  <si>
+    <t>SPK音腔</t>
+  </si>
+  <si>
+    <t>magnet</t>
   </si>
   <si>
     <t>LCM组件建模规范-LCD</t>
@@ -1269,7 +1429,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1307,16 +1467,23 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF2D3748"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF2D3748"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1678,7 +1845,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1722,6 +1889,66 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD7EDE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD7EDE8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD7EDE8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD7EDE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD7EDE8"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD7EDE8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD7EDE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD7EDE8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD7EDE8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1826,31 +2053,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1859,119 +2083,122 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1990,17 +2217,77 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2356,7 +2643,8 @@
     <col min="3" max="3" width="25.1818181818182" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="7" width="15" customWidth="1"/>
+    <col min="6" max="6" width="15" style="22" customWidth="1"/>
+    <col min="7" max="7" width="17.9090909090909" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7">
@@ -2367,7 +2655,7 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
+      <c r="F1" s="27"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7">
@@ -2386,7 +2674,7 @@
       <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="25" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="5" t="s">
@@ -2394,245 +2682,245 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:7">
-      <c r="A3" s="6">
+      <c r="A3" s="21">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="15">
         <v>0.5</v>
       </c>
-      <c r="G3" s="7"/>
+      <c r="G3" s="14"/>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7">
-      <c r="A4" s="6">
+      <c r="A4" s="21">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="15">
         <v>0.5</v>
       </c>
-      <c r="G4" s="7"/>
+      <c r="G4" s="14"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:7">
-      <c r="A5" s="6">
+      <c r="A5" s="21">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="15">
         <v>0.5</v>
       </c>
-      <c r="G5" s="7"/>
+      <c r="G5" s="14"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:7">
-      <c r="A6" s="6">
+      <c r="A6" s="21">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="15">
         <v>0.5</v>
       </c>
-      <c r="G6" s="7"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:7">
-      <c r="A7" s="6">
+      <c r="A7" s="21">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="D7" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="15">
         <v>0.5</v>
       </c>
-      <c r="G7" s="7"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:7">
-      <c r="A8" s="6">
+      <c r="A8" s="21">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="15">
         <v>0.5</v>
       </c>
-      <c r="G8" s="7"/>
+      <c r="G8" s="14"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:7">
-      <c r="A9" s="6">
+      <c r="A9" s="21">
         <v>7</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="D9" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="15">
         <v>0.3</v>
       </c>
-      <c r="G9" s="7"/>
+      <c r="G9" s="14"/>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:7">
-      <c r="A10" s="6">
+      <c r="A10" s="21">
         <v>8</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="15">
         <v>0.2</v>
       </c>
-      <c r="G10" s="7"/>
+      <c r="G10" s="14"/>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:7">
-      <c r="A11" s="6">
+      <c r="A11" s="21">
         <v>9</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="15">
         <v>0.5</v>
       </c>
-      <c r="G11" s="7"/>
+      <c r="G11" s="14"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:7">
-      <c r="A12" s="6">
+      <c r="A12" s="21">
         <v>10</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="15">
         <v>0.15</v>
       </c>
-      <c r="G12" s="7"/>
+      <c r="G12" s="14"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:7">
-      <c r="A13" s="6">
+      <c r="A13" s="21">
         <v>11</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="D13" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="6" t="s">
+      <c r="F13" s="15"/>
+      <c r="G13" s="14" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:7">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="11"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="31"/>
       <c r="G14" s="4"/>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7">
@@ -2651,7 +2939,7 @@
       <c r="E15" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="25" t="s">
         <v>6</v>
       </c>
       <c r="G15" s="5" t="s">
@@ -2659,345 +2947,345 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:7">
-      <c r="A16" s="6">
+      <c r="A16" s="21">
         <v>1</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="15">
         <v>0.5</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="14" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:7">
-      <c r="A17" s="6">
+      <c r="A17" s="21">
         <v>2</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="6" t="s">
+      <c r="D17" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="15">
         <v>0.3</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="14" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:7">
-      <c r="A18" s="6">
+      <c r="A18" s="21">
         <v>3</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="D18" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="15">
         <v>0.3</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="14" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7">
-      <c r="A19" s="6">
+      <c r="A19" s="21">
         <v>4</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="15">
         <v>0.5</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="14" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:7">
-      <c r="A20" s="6">
+      <c r="A20" s="21">
         <v>5</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="15">
         <v>0.5</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="14" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:7">
-      <c r="A21" s="6">
+      <c r="A21" s="21">
         <v>6</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="6" t="s">
+      <c r="F21" s="15"/>
+      <c r="G21" s="14" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:7">
-      <c r="A22" s="6">
+      <c r="A22" s="21">
         <v>7</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="6" t="s">
+      <c r="D22" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="14" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:7">
-      <c r="A23" s="6">
+      <c r="A23" s="21">
         <v>8</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="D23" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="14" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:7">
-      <c r="A24" s="6">
+      <c r="A24" s="21">
         <v>9</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="15">
         <v>0.5</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="14" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:7">
-      <c r="A25" s="6">
+      <c r="A25" s="21">
         <v>10</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="15">
         <v>0.5</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="14" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:7">
-      <c r="A26" s="6">
+      <c r="A26" s="21">
         <v>11</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="15">
         <v>0.5</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="14" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:7">
-      <c r="A27" s="6">
+      <c r="A27" s="21">
         <v>12</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="15">
         <v>0.5</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:7">
-      <c r="A28" s="6">
+      <c r="A28" s="21">
         <v>13</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="15">
         <v>0.5</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="14" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:7">
-      <c r="A29" s="6">
+      <c r="A29" s="21">
         <v>14</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="15">
         <v>0.5</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="14" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:7">
-      <c r="A30" s="6">
+      <c r="A30" s="21">
         <v>15</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="14" t="s">
         <v>90</v>
       </c>
     </row>
@@ -3025,7 +3313,8 @@
     <col min="3" max="3" width="24.2727272727273" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="6" max="6" width="13.1818181818182" style="22" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7">
@@ -3036,10 +3325,10 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
+      <c r="F1" s="27"/>
       <c r="G1" s="4"/>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:7">
+    <row r="2" spans="1:7">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -3055,7 +3344,7 @@
       <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="25" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="5" t="s">
@@ -3063,308 +3352,308 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:7">
-      <c r="A3" s="6">
+      <c r="A3" s="21">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="F3" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7">
+      <c r="A4" s="21">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="E4" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="15">
         <v>0.5</v>
       </c>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:7">
-      <c r="A4" s="6">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:7">
+      <c r="A5" s="21">
+        <v>3</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="C5" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E5" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F5" s="15">
         <v>0.5</v>
       </c>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:7">
-      <c r="A5" s="6">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:7">
+      <c r="A6" s="21">
+        <v>4</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="C6" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E6" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F6" s="15">
         <v>0.5</v>
       </c>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:7">
-      <c r="A6" s="6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:7">
+      <c r="A7" s="21">
+        <v>5</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="C7" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E7" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F7" s="15">
         <v>0.5</v>
       </c>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:7">
-      <c r="A7" s="6">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:7">
+      <c r="A8" s="21">
+        <v>6</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="C8" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E8" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F8" s="15">
         <v>0.5</v>
       </c>
-      <c r="G7" s="7"/>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:7">
-      <c r="A8" s="6">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:7">
+      <c r="A9" s="21">
+        <v>7</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="C9" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E9" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F9" s="15">
         <v>0.5</v>
       </c>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:7">
-      <c r="A9" s="6">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:7">
+      <c r="A10" s="21">
+        <v>8</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="C10" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E10" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F10" s="15">
         <v>0.5</v>
       </c>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:7">
-      <c r="A10" s="6">
-        <v>8</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C10" s="6" t="s">
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:7">
+      <c r="A11" s="21">
+        <v>9</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="C11" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:7">
+      <c r="A12" s="21">
         <v>10</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="B12" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="15">
         <v>0.5</v>
       </c>
-      <c r="G10" s="7"/>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:7">
-      <c r="A11" s="6">
-        <v>9</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:7">
+      <c r="A13" s="21">
+        <v>11</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="15">
         <v>0.5</v>
       </c>
-      <c r="G11" s="7"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:7">
-      <c r="A12" s="6">
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:7">
+      <c r="A14" s="21">
+        <v>12</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" s="6" t="s">
+      <c r="E14" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:7">
+      <c r="A15" s="21">
+        <v>13</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:7">
+      <c r="A16" s="21">
+        <v>14</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G12" s="7"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:7">
-      <c r="A13" s="6">
-        <v>11</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G13" s="7"/>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:7">
-      <c r="A14" s="6">
-        <v>12</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G14" s="7"/>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:7">
-      <c r="A15" s="6">
-        <v>13</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G15" s="7"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:7">
-      <c r="A16" s="6">
-        <v>14</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="E16" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:7">
+      <c r="A17" s="28" t="s">
         <v>121</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="G16" s="7"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:7">
-      <c r="A17" s="8" t="s">
-        <v>122</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="3"/>
+      <c r="F17" s="27"/>
       <c r="G17" s="4"/>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:7">
@@ -3383,7 +3672,7 @@
       <c r="E18" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="25" t="s">
         <v>6</v>
       </c>
       <c r="G18" s="5" t="s">
@@ -3391,211 +3680,211 @@
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7">
-      <c r="A19" s="6">
+      <c r="A19" s="21">
         <v>1</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="D19" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:7">
+      <c r="A20" s="21">
+        <v>2</v>
+      </c>
+      <c r="B20" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="C20" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E20" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:7">
+      <c r="A21" s="21">
+        <v>3</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:7">
+      <c r="A22" s="21">
+        <v>4</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="G19" s="7"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:7">
-      <c r="A20" s="6">
-        <v>2</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" s="6" t="s">
+      <c r="F22" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:7">
+      <c r="A23" s="21">
+        <v>5</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="F20" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="G20" s="7"/>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:7">
-      <c r="A21" s="6">
-        <v>3</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D21" s="6" t="s">
+      <c r="E23" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:7">
+      <c r="A24" s="21">
+        <v>6</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" s="6">
+      <c r="E24" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="15">
         <v>0.2</v>
       </c>
-      <c r="G21" s="7"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:7">
-      <c r="A22" s="6">
-        <v>4</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D22" s="6" t="s">
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:7">
+      <c r="A25" s="21">
+        <v>7</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E25" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="F25" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:7">
+      <c r="A26" s="21">
+        <v>8</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:7">
+      <c r="A27" s="21">
+        <v>9</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F27" s="15">
         <v>0.2</v>
       </c>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:7">
-      <c r="A23" s="6">
-        <v>5</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="D23" s="6" t="s">
+      <c r="G27" s="7"/>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:7">
+      <c r="A28" s="21">
+        <v>10</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D28" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="G23" s="7"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:7">
-      <c r="A24" s="6">
-        <v>6</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:7">
-      <c r="A25" s="6">
-        <v>7</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C25" s="6" t="s">
+      <c r="E28" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="F25" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="G25" s="7"/>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:7">
-      <c r="A26" s="6">
-        <v>8</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="G26" s="7"/>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:7">
-      <c r="A27" s="6">
-        <v>9</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="G27" s="7"/>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:7">
-      <c r="A28" s="6">
-        <v>10</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="F28" s="6">
+      <c r="F28" s="15">
         <v>0.2</v>
       </c>
       <c r="G28" s="7"/>
@@ -3619,7 +3908,7 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="1" max="1" width="11" style="22" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
@@ -3629,17 +3918,17 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
+        <v>144</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="24"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -3662,190 +3951,190 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:7">
-      <c r="A3" s="6">
+      <c r="A3" s="26">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7">
+      <c r="A4" s="26">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="C4" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F4" s="14">
         <v>0.3</v>
       </c>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:7">
-      <c r="A4" s="6">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:7">
+      <c r="A5" s="26">
+        <v>3</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="C5" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="F5" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:7">
+      <c r="A6" s="26">
+        <v>4</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:7">
+      <c r="A7" s="26">
+        <v>5</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="F7" s="14">
         <v>0.3</v>
       </c>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:7">
-      <c r="A5" s="6">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="F5" s="6">
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:7">
+      <c r="A8" s="26">
+        <v>6</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="14">
         <v>0.2</v>
       </c>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:7">
-      <c r="A6" s="6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:7">
+      <c r="A9" s="26">
+        <v>7</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:7">
+      <c r="A10" s="26">
+        <v>8</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="E10" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="F10" s="14">
         <v>0.2</v>
       </c>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:7">
-      <c r="A7" s="6">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="G7" s="7"/>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:7">
-      <c r="A8" s="6">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:7">
-      <c r="A9" s="6">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:7">
+      <c r="A11" s="26">
+        <v>9</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:7">
-      <c r="A10" s="6">
-        <v>8</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="F10" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="G10" s="7"/>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:7">
-      <c r="A11" s="6">
-        <v>9</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="F11" s="14">
         <v>0.2</v>
       </c>
       <c r="G11" s="7"/>
@@ -3865,7 +4154,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3878,33 +4167,33 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
+      <c r="A1" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="12" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="5" t="s">
@@ -3912,668 +4201,827 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:7">
-      <c r="A3" s="6">
+      <c r="A3" s="21">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="F3" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7">
+      <c r="A4" s="21">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="E4" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="F4" s="15">
         <v>0.8</v>
       </c>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:7">
-      <c r="A4" s="6">
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:7">
+      <c r="A5" s="21">
+        <v>3</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="F5" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:7">
+      <c r="A6" s="21">
+        <v>4</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:7">
+      <c r="A7" s="21">
+        <v>5</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F7" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:7">
+      <c r="A8" s="21">
+        <v>6</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="F8" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:7">
+      <c r="A9" s="21">
+        <v>7</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="F9" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:7">
+      <c r="A10" s="21">
+        <v>8</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="F10" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:7">
+      <c r="A11" s="21">
+        <v>9</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="F11" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:7">
+      <c r="A12" s="21">
+        <v>10</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="F12" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:7">
+      <c r="A13" s="21">
+        <v>11</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="F13" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:7">
+      <c r="A14" s="21">
+        <v>12</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:7">
+      <c r="A15" s="21">
+        <v>13</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="F15" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:7">
+      <c r="A16" s="21">
+        <v>14</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F16" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:7">
+      <c r="A17" s="21">
+        <v>15</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F17" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:7">
+      <c r="A18" s="21">
+        <v>16</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="F18" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:7">
+      <c r="A19" s="21">
+        <v>17</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="F19" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:7">
+      <c r="A20" s="21">
+        <v>18</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F20" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:7">
+      <c r="A21" s="21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F21" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:7">
+      <c r="A22" s="21">
+        <v>20</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="F22" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:7">
+      <c r="A23" s="21">
+        <v>20</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="F23" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:7">
+      <c r="A24" s="21">
+        <v>21</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F24" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:7">
+      <c r="A25" s="21">
+        <v>22</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="F25" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:7">
+      <c r="A26" s="21">
+        <v>23</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="F26" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:7">
+      <c r="A27" s="21">
+        <v>24</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="F27" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="G27" s="7"/>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:7">
+      <c r="A28" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:7">
+      <c r="A29" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:7">
-      <c r="A5" s="6">
+      <c r="C29" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:7">
-      <c r="A6" s="6">
+      <c r="D29" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:7">
-      <c r="A7" s="6">
+      <c r="E29" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="F29" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G29" s="7"/>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:7">
+      <c r="A30" s="21">
+        <v>1</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F30" s="15">
         <v>0.5</v>
       </c>
-      <c r="G7" s="7"/>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:7">
-      <c r="A8" s="6">
+      <c r="G30" s="7"/>
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="1:7">
+      <c r="A31" s="21">
+        <v>2</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F31" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G31" s="7"/>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:7">
+      <c r="A32" s="21">
+        <v>3</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="F32" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G32" s="7"/>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:7">
+      <c r="A33" s="21">
+        <v>4</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="F33" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G33" s="7"/>
+    </row>
+    <row r="34" ht="24" customHeight="1" spans="1:7">
+      <c r="A34" s="21">
+        <v>5</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F34" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G34" s="7"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="21">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="B35" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="F35" s="15">
         <v>0.5</v>
       </c>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:7">
-      <c r="A9" s="6">
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="21">
         <v>7</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="F9" s="6">
+      <c r="B36" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36" s="15">
         <v>0.5</v>
       </c>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:7">
-      <c r="A10" s="6">
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="21">
         <v>8</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="B37" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="F37" s="15">
         <v>0.5</v>
       </c>
-      <c r="G10" s="7"/>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:7">
-      <c r="A11" s="6">
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="21">
         <v>9</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="B38" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F38" s="15">
         <v>0.5</v>
       </c>
-      <c r="G11" s="7"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:7">
-      <c r="A12" s="6">
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="21">
         <v>10</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="F12" s="6">
+      <c r="B39" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="F39" s="15">
         <v>0.5</v>
       </c>
-      <c r="G12" s="7"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:7">
-      <c r="A13" s="6">
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="21">
         <v>11</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F13" s="6">
+      <c r="B40" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F40" s="15">
         <v>0.5</v>
       </c>
-      <c r="G13" s="7"/>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:7">
-      <c r="A14" s="6">
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="21">
         <v>12</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F14" s="6">
+      <c r="B41" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="F41" s="15">
         <v>0.5</v>
       </c>
-      <c r="G14" s="7"/>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:7">
-      <c r="A15" s="6">
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="21">
         <v>13</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="F15" s="6">
+      <c r="B42" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="F42" s="15">
         <v>0.5</v>
       </c>
-      <c r="G15" s="7"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:7">
-      <c r="A16" s="6">
-        <v>14</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="F16" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G16" s="7"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:7">
-      <c r="A17" s="6">
-        <v>15</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F17" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G17" s="7"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:7">
-      <c r="A18" s="6">
-        <v>16</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F18" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G18" s="7"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:7">
-      <c r="A19" s="6">
-        <v>17</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="F19" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G19" s="7"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:7">
-      <c r="A20" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="4"/>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:7">
-      <c r="A21" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:7">
-      <c r="A22" s="6">
-        <v>1</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F22" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:7">
-      <c r="A23" s="6">
-        <v>2</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F23" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G23" s="7"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:7">
-      <c r="A24" s="6">
-        <v>3</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="F24" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:7">
-      <c r="A25" s="6">
-        <v>4</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="F25" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G25" s="7"/>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:7">
-      <c r="A26" s="6">
-        <v>5</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F26" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G26" s="7"/>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:7">
-      <c r="A27" s="6">
-        <v>6</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="F27" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G27" s="7"/>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:7">
-      <c r="A28" s="6">
-        <v>7</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="1:7">
-      <c r="A29" s="6">
-        <v>8</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="F29" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G29" s="7"/>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="1:7">
-      <c r="A30" s="6">
-        <v>9</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F30" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G30" s="7"/>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="1:7">
-      <c r="A31" s="6">
-        <v>10</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="F31" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G31" s="7"/>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:7">
-      <c r="A32" s="6">
-        <v>11</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G32" s="7"/>
-    </row>
-    <row r="33" ht="24" customHeight="1" spans="1:7">
-      <c r="A33" s="6">
-        <v>12</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="F33" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G33" s="7"/>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="1:7">
-      <c r="A34" s="6">
-        <v>13</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="F34" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G34" s="7"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:F34" etc:filterBottomFollowUsedRange="0">
@@ -4581,7 +5029,7 @@
   </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A28:F28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -4591,504 +5039,2278 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="18.8181818181818" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="5" max="5" width="29.1818181818182" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
+      <c r="A1" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:7">
-      <c r="A3" s="6">
+      <c r="A3" s="13">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="B3" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="F3" s="15">
+        <v>0.6</v>
+      </c>
+      <c r="G3" s="14"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:7">
+      <c r="A4" s="13">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="F4" s="15">
+        <v>0.6</v>
+      </c>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:7">
+      <c r="A5" s="13">
+        <v>3</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="F5" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:7">
+      <c r="A6" s="13">
+        <v>4</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="F6" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:7">
+      <c r="A7" s="13">
+        <v>5</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="F7" s="15">
         <v>0.5</v>
       </c>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:7">
-      <c r="A4" s="6">
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:7">
+      <c r="A8" s="13">
+        <v>6</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="F8" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:7">
+      <c r="A9" s="13">
+        <v>7</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F9" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:7">
+      <c r="A10" s="13">
+        <v>8</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="F10" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:7">
+      <c r="A11" s="13">
+        <v>9</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:7">
+      <c r="A12" s="13">
+        <v>10</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="G12" s="14"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:7">
+      <c r="A13" s="13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="F13" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G13" s="14"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:7">
+      <c r="A14" s="13">
+        <v>12</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="14"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:7">
+      <c r="A15" s="13">
+        <v>13</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="F15" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:7">
+      <c r="A16" s="13">
+        <v>14</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="G16" s="14"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:7">
+      <c r="A17" s="13">
+        <v>15</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="F17" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:7">
+      <c r="A18" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="19"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:7">
+      <c r="A19" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="C19" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:7">
+      <c r="A20" s="13">
+        <v>1</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="F20" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="G20" s="14"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:7">
+      <c r="A21" s="13">
+        <v>2</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="F21" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="G21" s="14"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:7">
+      <c r="A22" s="13">
+        <v>3</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="14"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:7">
+      <c r="A23" s="13">
+        <v>4</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="F23" s="17"/>
+      <c r="G23" s="14"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:7">
+      <c r="A24" s="13">
+        <v>5</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F24" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="14"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="13">
+        <v>6</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="F25" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G25" s="14"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="13">
+        <v>7</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="F26" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G26" s="14"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="13">
+        <v>8</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="F27" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="G27" s="14"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="13">
+        <v>9</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="F28" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="G28" s="16"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="13">
         <v>10</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0.6</v>
-      </c>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:7">
-      <c r="A5" s="6">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0.6</v>
-      </c>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:7">
-      <c r="A6" s="6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="B29" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="D29" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:7">
-      <c r="A7" s="6">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="E29" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="F29" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="G29" s="16"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="13">
+        <v>11</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="F30" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="G30" s="16"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="13">
+        <v>12</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="F31" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="G31" s="16"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="13">
+        <v>13</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="F32" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="G32" s="16"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="13">
+        <v>14</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="F33" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="G33" s="16"/>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="13">
+        <v>15</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="F34" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="G34" s="16"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="13">
+        <v>16</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="F35" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="13">
+        <v>17</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="F36" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="G36" s="16"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="13">
+        <v>18</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="F37" s="15">
         <v>0.5</v>
       </c>
-      <c r="G7" s="7"/>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:7">
-      <c r="A8" s="6">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:7">
-      <c r="A9" s="6">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:7">
-      <c r="A10" s="6">
-        <v>8</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F10" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G10" s="7"/>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:7">
-      <c r="A11" s="6">
-        <v>9</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G11" s="7"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:7">
-      <c r="A12" s="6">
-        <v>10</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="F12" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G12" s="7"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:7">
-      <c r="A13" s="6">
-        <v>11</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G13" s="7"/>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:7">
-      <c r="A14" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:7">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:7">
-      <c r="A16" s="6">
-        <v>1</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="F16" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="G16" s="7"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:7">
-      <c r="A17" s="6">
-        <v>2</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G17" s="7"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:7">
-      <c r="A18" s="6">
-        <v>3</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F18" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G18" s="7"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:7">
-      <c r="A19" s="6">
-        <v>4</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="F19" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G19" s="7"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:7">
-      <c r="A20" s="6">
-        <v>5</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="F20" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="G20" s="7"/>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:7">
-      <c r="A21" s="6">
-        <v>6</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="F21" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="G21" s="7"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:7">
-      <c r="A22" s="6">
-        <v>7</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="F22" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:7">
-      <c r="A23" s="6">
-        <v>8</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="F23" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="G23" s="7"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:7">
-      <c r="A24" s="6">
-        <v>9</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="F24" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="G24" s="7"/>
+      <c r="G37" s="16"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="16"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="16"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="16"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="16"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="16"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="16"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="16"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="16"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="16"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="16"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="16"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="16"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="16"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="16"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="16"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="16"/>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="16"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="16"/>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="16"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="16"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="16"/>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="16"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="16"/>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="16"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="16"/>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="16"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="16"/>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="16"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="16"/>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="16"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="16"/>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="16"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="16"/>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="16"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="16"/>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="16"/>
+      <c r="B56" s="16"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="16"/>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="16"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="16"/>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="16"/>
+      <c r="B58" s="16"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="16"/>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="16"/>
+      <c r="B59" s="16"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="16"/>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="16"/>
+      <c r="B60" s="16"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="16"/>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="16"/>
+      <c r="B61" s="16"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="16"/>
+      <c r="F61" s="17"/>
+      <c r="G61" s="16"/>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="16"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="16"/>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="16"/>
+      <c r="B63" s="16"/>
+      <c r="C63" s="16"/>
+      <c r="D63" s="16"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="16"/>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="16"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="17"/>
+      <c r="G64" s="16"/>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="16"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="17"/>
+      <c r="G65" s="16"/>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="16"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="16"/>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="16"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="16"/>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="16"/>
+      <c r="B68" s="16"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="16"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="16"/>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="16"/>
+      <c r="B69" s="16"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="17"/>
+      <c r="G69" s="16"/>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="16"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="17"/>
+      <c r="G70" s="16"/>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="16"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="17"/>
+      <c r="G71" s="16"/>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="16"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="17"/>
+      <c r="G72" s="16"/>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="16"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="16"/>
+      <c r="F73" s="17"/>
+      <c r="G73" s="16"/>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="16"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="17"/>
+      <c r="G74" s="16"/>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="16"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="17"/>
+      <c r="G75" s="16"/>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="16"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="17"/>
+      <c r="G76" s="16"/>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="16"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="17"/>
+      <c r="G77" s="16"/>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="16"/>
+      <c r="B78" s="16"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="17"/>
+      <c r="G78" s="16"/>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="16"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="17"/>
+      <c r="G79" s="16"/>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="16"/>
+      <c r="B80" s="16"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="16"/>
+      <c r="F80" s="17"/>
+      <c r="G80" s="16"/>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="16"/>
+      <c r="B81" s="16"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="16"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="16"/>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="16"/>
+      <c r="B82" s="16"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="16"/>
+      <c r="E82" s="16"/>
+      <c r="F82" s="17"/>
+      <c r="G82" s="16"/>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="16"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16"/>
+      <c r="F83" s="17"/>
+      <c r="G83" s="16"/>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="16"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="16"/>
+      <c r="F84" s="17"/>
+      <c r="G84" s="16"/>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="16"/>
+      <c r="B85" s="16"/>
+      <c r="C85" s="16"/>
+      <c r="D85" s="16"/>
+      <c r="E85" s="16"/>
+      <c r="F85" s="17"/>
+      <c r="G85" s="16"/>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="16"/>
+      <c r="B86" s="16"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="16"/>
+      <c r="E86" s="16"/>
+      <c r="F86" s="17"/>
+      <c r="G86" s="16"/>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="16"/>
+      <c r="B87" s="16"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="16"/>
+      <c r="F87" s="17"/>
+      <c r="G87" s="16"/>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="16"/>
+      <c r="B88" s="16"/>
+      <c r="C88" s="16"/>
+      <c r="D88" s="16"/>
+      <c r="E88" s="16"/>
+      <c r="F88" s="17"/>
+      <c r="G88" s="16"/>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="16"/>
+      <c r="B89" s="16"/>
+      <c r="C89" s="16"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="16"/>
+      <c r="F89" s="17"/>
+      <c r="G89" s="16"/>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="16"/>
+      <c r="B90" s="16"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="16"/>
+      <c r="F90" s="17"/>
+      <c r="G90" s="16"/>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="16"/>
+      <c r="B91" s="16"/>
+      <c r="C91" s="16"/>
+      <c r="D91" s="16"/>
+      <c r="E91" s="16"/>
+      <c r="F91" s="17"/>
+      <c r="G91" s="16"/>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="16"/>
+      <c r="B92" s="16"/>
+      <c r="C92" s="16"/>
+      <c r="D92" s="16"/>
+      <c r="E92" s="16"/>
+      <c r="F92" s="17"/>
+      <c r="G92" s="16"/>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="16"/>
+      <c r="B93" s="16"/>
+      <c r="C93" s="16"/>
+      <c r="D93" s="16"/>
+      <c r="E93" s="16"/>
+      <c r="F93" s="17"/>
+      <c r="G93" s="16"/>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="16"/>
+      <c r="B94" s="16"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="16"/>
+      <c r="E94" s="16"/>
+      <c r="F94" s="17"/>
+      <c r="G94" s="16"/>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="16"/>
+      <c r="B95" s="16"/>
+      <c r="C95" s="16"/>
+      <c r="D95" s="16"/>
+      <c r="E95" s="16"/>
+      <c r="F95" s="17"/>
+      <c r="G95" s="16"/>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="16"/>
+      <c r="B96" s="16"/>
+      <c r="C96" s="16"/>
+      <c r="D96" s="16"/>
+      <c r="E96" s="16"/>
+      <c r="F96" s="17"/>
+      <c r="G96" s="16"/>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" s="16"/>
+      <c r="B97" s="16"/>
+      <c r="C97" s="16"/>
+      <c r="D97" s="16"/>
+      <c r="E97" s="16"/>
+      <c r="F97" s="17"/>
+      <c r="G97" s="16"/>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="16"/>
+      <c r="B98" s="16"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="16"/>
+      <c r="E98" s="16"/>
+      <c r="F98" s="17"/>
+      <c r="G98" s="16"/>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="16"/>
+      <c r="B99" s="16"/>
+      <c r="C99" s="16"/>
+      <c r="D99" s="16"/>
+      <c r="E99" s="16"/>
+      <c r="F99" s="17"/>
+      <c r="G99" s="16"/>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="16"/>
+      <c r="B100" s="16"/>
+      <c r="C100" s="16"/>
+      <c r="D100" s="16"/>
+      <c r="E100" s="16"/>
+      <c r="F100" s="17"/>
+      <c r="G100" s="16"/>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="16"/>
+      <c r="B101" s="16"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="16"/>
+      <c r="F101" s="17"/>
+      <c r="G101" s="16"/>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="16"/>
+      <c r="B102" s="16"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="16"/>
+      <c r="F102" s="17"/>
+      <c r="G102" s="16"/>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="16"/>
+      <c r="B103" s="16"/>
+      <c r="C103" s="16"/>
+      <c r="D103" s="16"/>
+      <c r="E103" s="16"/>
+      <c r="F103" s="17"/>
+      <c r="G103" s="16"/>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" s="16"/>
+      <c r="B104" s="16"/>
+      <c r="C104" s="16"/>
+      <c r="D104" s="16"/>
+      <c r="E104" s="16"/>
+      <c r="F104" s="17"/>
+      <c r="G104" s="16"/>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" s="16"/>
+      <c r="B105" s="16"/>
+      <c r="C105" s="16"/>
+      <c r="D105" s="16"/>
+      <c r="E105" s="16"/>
+      <c r="F105" s="17"/>
+      <c r="G105" s="16"/>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" s="16"/>
+      <c r="B106" s="16"/>
+      <c r="C106" s="16"/>
+      <c r="D106" s="16"/>
+      <c r="E106" s="16"/>
+      <c r="F106" s="17"/>
+      <c r="G106" s="16"/>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" s="16"/>
+      <c r="B107" s="16"/>
+      <c r="C107" s="16"/>
+      <c r="D107" s="16"/>
+      <c r="E107" s="16"/>
+      <c r="F107" s="17"/>
+      <c r="G107" s="16"/>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" s="16"/>
+      <c r="B108" s="16"/>
+      <c r="C108" s="16"/>
+      <c r="D108" s="16"/>
+      <c r="E108" s="16"/>
+      <c r="F108" s="17"/>
+      <c r="G108" s="16"/>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" s="16"/>
+      <c r="B109" s="16"/>
+      <c r="C109" s="16"/>
+      <c r="D109" s="16"/>
+      <c r="E109" s="16"/>
+      <c r="F109" s="17"/>
+      <c r="G109" s="16"/>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" s="16"/>
+      <c r="B110" s="16"/>
+      <c r="C110" s="16"/>
+      <c r="D110" s="16"/>
+      <c r="E110" s="16"/>
+      <c r="F110" s="17"/>
+      <c r="G110" s="16"/>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" s="16"/>
+      <c r="B111" s="16"/>
+      <c r="C111" s="16"/>
+      <c r="D111" s="16"/>
+      <c r="E111" s="16"/>
+      <c r="F111" s="17"/>
+      <c r="G111" s="16"/>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" s="16"/>
+      <c r="B112" s="16"/>
+      <c r="C112" s="16"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="16"/>
+      <c r="F112" s="17"/>
+      <c r="G112" s="16"/>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="16"/>
+      <c r="B113" s="16"/>
+      <c r="C113" s="16"/>
+      <c r="D113" s="16"/>
+      <c r="E113" s="16"/>
+      <c r="F113" s="17"/>
+      <c r="G113" s="16"/>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" s="16"/>
+      <c r="B114" s="16"/>
+      <c r="C114" s="16"/>
+      <c r="D114" s="16"/>
+      <c r="E114" s="16"/>
+      <c r="F114" s="17"/>
+      <c r="G114" s="16"/>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="16"/>
+      <c r="B115" s="16"/>
+      <c r="C115" s="16"/>
+      <c r="D115" s="16"/>
+      <c r="E115" s="16"/>
+      <c r="F115" s="17"/>
+      <c r="G115" s="16"/>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="16"/>
+      <c r="B116" s="16"/>
+      <c r="C116" s="16"/>
+      <c r="D116" s="16"/>
+      <c r="E116" s="16"/>
+      <c r="F116" s="17"/>
+      <c r="G116" s="16"/>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="16"/>
+      <c r="B117" s="16"/>
+      <c r="C117" s="16"/>
+      <c r="D117" s="16"/>
+      <c r="E117" s="16"/>
+      <c r="F117" s="17"/>
+      <c r="G117" s="16"/>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="16"/>
+      <c r="B118" s="16"/>
+      <c r="C118" s="16"/>
+      <c r="D118" s="16"/>
+      <c r="E118" s="16"/>
+      <c r="F118" s="17"/>
+      <c r="G118" s="16"/>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="16"/>
+      <c r="B119" s="16"/>
+      <c r="C119" s="16"/>
+      <c r="D119" s="16"/>
+      <c r="E119" s="16"/>
+      <c r="F119" s="17"/>
+      <c r="G119" s="16"/>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" s="16"/>
+      <c r="B120" s="16"/>
+      <c r="C120" s="16"/>
+      <c r="D120" s="16"/>
+      <c r="E120" s="16"/>
+      <c r="F120" s="17"/>
+      <c r="G120" s="16"/>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" s="16"/>
+      <c r="B121" s="16"/>
+      <c r="C121" s="16"/>
+      <c r="D121" s="16"/>
+      <c r="E121" s="16"/>
+      <c r="F121" s="17"/>
+      <c r="G121" s="16"/>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" s="16"/>
+      <c r="B122" s="16"/>
+      <c r="C122" s="16"/>
+      <c r="D122" s="16"/>
+      <c r="E122" s="16"/>
+      <c r="F122" s="17"/>
+      <c r="G122" s="16"/>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" s="16"/>
+      <c r="B123" s="16"/>
+      <c r="C123" s="16"/>
+      <c r="D123" s="16"/>
+      <c r="E123" s="16"/>
+      <c r="F123" s="17"/>
+      <c r="G123" s="16"/>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" s="16"/>
+      <c r="B124" s="16"/>
+      <c r="C124" s="16"/>
+      <c r="D124" s="16"/>
+      <c r="E124" s="16"/>
+      <c r="F124" s="17"/>
+      <c r="G124" s="16"/>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" s="16"/>
+      <c r="B125" s="16"/>
+      <c r="C125" s="16"/>
+      <c r="D125" s="16"/>
+      <c r="E125" s="16"/>
+      <c r="F125" s="17"/>
+      <c r="G125" s="16"/>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" s="16"/>
+      <c r="B126" s="16"/>
+      <c r="C126" s="16"/>
+      <c r="D126" s="16"/>
+      <c r="E126" s="16"/>
+      <c r="F126" s="17"/>
+      <c r="G126" s="16"/>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" s="16"/>
+      <c r="B127" s="16"/>
+      <c r="C127" s="16"/>
+      <c r="D127" s="16"/>
+      <c r="E127" s="16"/>
+      <c r="F127" s="17"/>
+      <c r="G127" s="16"/>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" s="16"/>
+      <c r="B128" s="16"/>
+      <c r="C128" s="16"/>
+      <c r="D128" s="16"/>
+      <c r="E128" s="16"/>
+      <c r="F128" s="17"/>
+      <c r="G128" s="16"/>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" s="16"/>
+      <c r="B129" s="16"/>
+      <c r="C129" s="16"/>
+      <c r="D129" s="16"/>
+      <c r="E129" s="16"/>
+      <c r="F129" s="17"/>
+      <c r="G129" s="16"/>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" s="16"/>
+      <c r="B130" s="16"/>
+      <c r="C130" s="16"/>
+      <c r="D130" s="16"/>
+      <c r="E130" s="16"/>
+      <c r="F130" s="17"/>
+      <c r="G130" s="16"/>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" s="16"/>
+      <c r="B131" s="16"/>
+      <c r="C131" s="16"/>
+      <c r="D131" s="16"/>
+      <c r="E131" s="16"/>
+      <c r="F131" s="17"/>
+      <c r="G131" s="16"/>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" s="16"/>
+      <c r="B132" s="16"/>
+      <c r="C132" s="16"/>
+      <c r="D132" s="16"/>
+      <c r="E132" s="16"/>
+      <c r="F132" s="17"/>
+      <c r="G132" s="16"/>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" s="16"/>
+      <c r="B133" s="16"/>
+      <c r="C133" s="16"/>
+      <c r="D133" s="16"/>
+      <c r="E133" s="16"/>
+      <c r="F133" s="17"/>
+      <c r="G133" s="16"/>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" s="16"/>
+      <c r="B134" s="16"/>
+      <c r="C134" s="16"/>
+      <c r="D134" s="16"/>
+      <c r="E134" s="16"/>
+      <c r="F134" s="17"/>
+      <c r="G134" s="16"/>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" s="16"/>
+      <c r="B135" s="16"/>
+      <c r="C135" s="16"/>
+      <c r="D135" s="16"/>
+      <c r="E135" s="16"/>
+      <c r="F135" s="17"/>
+      <c r="G135" s="16"/>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" s="16"/>
+      <c r="B136" s="16"/>
+      <c r="C136" s="16"/>
+      <c r="D136" s="16"/>
+      <c r="E136" s="16"/>
+      <c r="F136" s="17"/>
+      <c r="G136" s="16"/>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" s="16"/>
+      <c r="B137" s="16"/>
+      <c r="C137" s="16"/>
+      <c r="D137" s="16"/>
+      <c r="E137" s="16"/>
+      <c r="F137" s="17"/>
+      <c r="G137" s="16"/>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" s="16"/>
+      <c r="B138" s="16"/>
+      <c r="C138" s="16"/>
+      <c r="D138" s="16"/>
+      <c r="E138" s="16"/>
+      <c r="F138" s="17"/>
+      <c r="G138" s="16"/>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" s="16"/>
+      <c r="B139" s="16"/>
+      <c r="C139" s="16"/>
+      <c r="D139" s="16"/>
+      <c r="E139" s="16"/>
+      <c r="F139" s="17"/>
+      <c r="G139" s="16"/>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" s="16"/>
+      <c r="B140" s="16"/>
+      <c r="C140" s="16"/>
+      <c r="D140" s="16"/>
+      <c r="E140" s="16"/>
+      <c r="F140" s="17"/>
+      <c r="G140" s="16"/>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" s="16"/>
+      <c r="B141" s="16"/>
+      <c r="C141" s="16"/>
+      <c r="D141" s="16"/>
+      <c r="E141" s="16"/>
+      <c r="F141" s="17"/>
+      <c r="G141" s="16"/>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" s="16"/>
+      <c r="B142" s="16"/>
+      <c r="C142" s="16"/>
+      <c r="D142" s="16"/>
+      <c r="E142" s="16"/>
+      <c r="F142" s="17"/>
+      <c r="G142" s="16"/>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" s="16"/>
+      <c r="B143" s="16"/>
+      <c r="C143" s="16"/>
+      <c r="D143" s="16"/>
+      <c r="E143" s="16"/>
+      <c r="F143" s="17"/>
+      <c r="G143" s="16"/>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" s="16"/>
+      <c r="B144" s="16"/>
+      <c r="C144" s="16"/>
+      <c r="D144" s="16"/>
+      <c r="E144" s="16"/>
+      <c r="F144" s="17"/>
+      <c r="G144" s="16"/>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" s="16"/>
+      <c r="B145" s="16"/>
+      <c r="C145" s="16"/>
+      <c r="D145" s="16"/>
+      <c r="E145" s="16"/>
+      <c r="F145" s="17"/>
+      <c r="G145" s="16"/>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" s="16"/>
+      <c r="B146" s="16"/>
+      <c r="C146" s="16"/>
+      <c r="D146" s="16"/>
+      <c r="E146" s="16"/>
+      <c r="F146" s="17"/>
+      <c r="G146" s="16"/>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" s="16"/>
+      <c r="B147" s="16"/>
+      <c r="C147" s="16"/>
+      <c r="D147" s="16"/>
+      <c r="E147" s="16"/>
+      <c r="F147" s="17"/>
+      <c r="G147" s="16"/>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" s="16"/>
+      <c r="B148" s="16"/>
+      <c r="C148" s="16"/>
+      <c r="D148" s="16"/>
+      <c r="E148" s="16"/>
+      <c r="F148" s="17"/>
+      <c r="G148" s="16"/>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" s="16"/>
+      <c r="B149" s="16"/>
+      <c r="C149" s="16"/>
+      <c r="D149" s="16"/>
+      <c r="E149" s="16"/>
+      <c r="F149" s="17"/>
+      <c r="G149" s="16"/>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" s="16"/>
+      <c r="B150" s="16"/>
+      <c r="C150" s="16"/>
+      <c r="D150" s="16"/>
+      <c r="E150" s="16"/>
+      <c r="F150" s="17"/>
+      <c r="G150" s="16"/>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" s="16"/>
+      <c r="B151" s="16"/>
+      <c r="C151" s="16"/>
+      <c r="D151" s="16"/>
+      <c r="E151" s="16"/>
+      <c r="F151" s="17"/>
+      <c r="G151" s="16"/>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" s="16"/>
+      <c r="B152" s="16"/>
+      <c r="C152" s="16"/>
+      <c r="D152" s="16"/>
+      <c r="E152" s="16"/>
+      <c r="F152" s="17"/>
+      <c r="G152" s="16"/>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" s="16"/>
+      <c r="B153" s="16"/>
+      <c r="C153" s="16"/>
+      <c r="D153" s="16"/>
+      <c r="E153" s="16"/>
+      <c r="F153" s="17"/>
+      <c r="G153" s="16"/>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" s="16"/>
+      <c r="B154" s="16"/>
+      <c r="C154" s="16"/>
+      <c r="D154" s="16"/>
+      <c r="E154" s="16"/>
+      <c r="F154" s="17"/>
+      <c r="G154" s="16"/>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" s="16"/>
+      <c r="B155" s="16"/>
+      <c r="C155" s="16"/>
+      <c r="D155" s="16"/>
+      <c r="E155" s="16"/>
+      <c r="F155" s="17"/>
+      <c r="G155" s="16"/>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" s="16"/>
+      <c r="B156" s="16"/>
+      <c r="C156" s="16"/>
+      <c r="D156" s="16"/>
+      <c r="E156" s="16"/>
+      <c r="F156" s="17"/>
+      <c r="G156" s="16"/>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" s="16"/>
+      <c r="B157" s="16"/>
+      <c r="C157" s="16"/>
+      <c r="D157" s="16"/>
+      <c r="E157" s="16"/>
+      <c r="F157" s="17"/>
+      <c r="G157" s="16"/>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" s="16"/>
+      <c r="B158" s="16"/>
+      <c r="C158" s="16"/>
+      <c r="D158" s="16"/>
+      <c r="E158" s="16"/>
+      <c r="F158" s="17"/>
+      <c r="G158" s="16"/>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" s="16"/>
+      <c r="B159" s="16"/>
+      <c r="C159" s="16"/>
+      <c r="D159" s="16"/>
+      <c r="E159" s="16"/>
+      <c r="F159" s="17"/>
+      <c r="G159" s="16"/>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" s="16"/>
+      <c r="B160" s="16"/>
+      <c r="C160" s="16"/>
+      <c r="D160" s="16"/>
+      <c r="E160" s="16"/>
+      <c r="F160" s="17"/>
+      <c r="G160" s="16"/>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" s="16"/>
+      <c r="B161" s="16"/>
+      <c r="C161" s="16"/>
+      <c r="D161" s="16"/>
+      <c r="E161" s="16"/>
+      <c r="F161" s="17"/>
+      <c r="G161" s="16"/>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" s="16"/>
+      <c r="B162" s="16"/>
+      <c r="C162" s="16"/>
+      <c r="D162" s="16"/>
+      <c r="E162" s="16"/>
+      <c r="F162" s="17"/>
+      <c r="G162" s="16"/>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" s="16"/>
+      <c r="B163" s="16"/>
+      <c r="C163" s="16"/>
+      <c r="D163" s="16"/>
+      <c r="E163" s="16"/>
+      <c r="F163" s="17"/>
+      <c r="G163" s="16"/>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" s="16"/>
+      <c r="B164" s="16"/>
+      <c r="C164" s="16"/>
+      <c r="D164" s="16"/>
+      <c r="E164" s="16"/>
+      <c r="F164" s="17"/>
+      <c r="G164" s="16"/>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" s="16"/>
+      <c r="B165" s="16"/>
+      <c r="C165" s="16"/>
+      <c r="D165" s="16"/>
+      <c r="E165" s="16"/>
+      <c r="F165" s="17"/>
+      <c r="G165" s="16"/>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" s="16"/>
+      <c r="B166" s="16"/>
+      <c r="C166" s="16"/>
+      <c r="D166" s="16"/>
+      <c r="E166" s="16"/>
+      <c r="F166" s="17"/>
+      <c r="G166" s="16"/>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" s="16"/>
+      <c r="B167" s="16"/>
+      <c r="C167" s="16"/>
+      <c r="D167" s="16"/>
+      <c r="E167" s="16"/>
+      <c r="F167" s="17"/>
+      <c r="G167" s="16"/>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" s="16"/>
+      <c r="B168" s="16"/>
+      <c r="C168" s="16"/>
+      <c r="D168" s="16"/>
+      <c r="E168" s="16"/>
+      <c r="F168" s="17"/>
+      <c r="G168" s="16"/>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" s="16"/>
+      <c r="B169" s="16"/>
+      <c r="C169" s="16"/>
+      <c r="D169" s="16"/>
+      <c r="E169" s="16"/>
+      <c r="F169" s="17"/>
+      <c r="G169" s="16"/>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" s="16"/>
+      <c r="B170" s="16"/>
+      <c r="C170" s="16"/>
+      <c r="D170" s="16"/>
+      <c r="E170" s="16"/>
+      <c r="F170" s="17"/>
+      <c r="G170" s="16"/>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" s="16"/>
+      <c r="B171" s="16"/>
+      <c r="C171" s="16"/>
+      <c r="D171" s="16"/>
+      <c r="E171" s="16"/>
+      <c r="F171" s="17"/>
+      <c r="G171" s="16"/>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" s="16"/>
+      <c r="B172" s="16"/>
+      <c r="C172" s="16"/>
+      <c r="D172" s="16"/>
+      <c r="E172" s="16"/>
+      <c r="F172" s="17"/>
+      <c r="G172" s="16"/>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" s="16"/>
+      <c r="B173" s="16"/>
+      <c r="C173" s="16"/>
+      <c r="D173" s="16"/>
+      <c r="E173" s="16"/>
+      <c r="F173" s="17"/>
+      <c r="G173" s="16"/>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" s="16"/>
+      <c r="B174" s="16"/>
+      <c r="C174" s="16"/>
+      <c r="D174" s="16"/>
+      <c r="E174" s="16"/>
+      <c r="F174" s="17"/>
+      <c r="G174" s="16"/>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" s="16"/>
+      <c r="B175" s="16"/>
+      <c r="C175" s="16"/>
+      <c r="D175" s="16"/>
+      <c r="E175" s="16"/>
+      <c r="F175" s="17"/>
+      <c r="G175" s="16"/>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" s="16"/>
+      <c r="B176" s="16"/>
+      <c r="C176" s="16"/>
+      <c r="D176" s="16"/>
+      <c r="E176" s="16"/>
+      <c r="F176" s="17"/>
+      <c r="G176" s="16"/>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" s="16"/>
+      <c r="B177" s="16"/>
+      <c r="C177" s="16"/>
+      <c r="D177" s="16"/>
+      <c r="E177" s="16"/>
+      <c r="F177" s="17"/>
+      <c r="G177" s="16"/>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" s="16"/>
+      <c r="B178" s="16"/>
+      <c r="C178" s="16"/>
+      <c r="D178" s="16"/>
+      <c r="E178" s="16"/>
+      <c r="F178" s="17"/>
+      <c r="G178" s="16"/>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" s="16"/>
+      <c r="B179" s="16"/>
+      <c r="C179" s="16"/>
+      <c r="D179" s="16"/>
+      <c r="E179" s="16"/>
+      <c r="F179" s="17"/>
+      <c r="G179" s="16"/>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" s="16"/>
+      <c r="B180" s="16"/>
+      <c r="C180" s="16"/>
+      <c r="D180" s="16"/>
+      <c r="E180" s="16"/>
+      <c r="F180" s="17"/>
+      <c r="G180" s="16"/>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" s="16"/>
+      <c r="B181" s="16"/>
+      <c r="C181" s="16"/>
+      <c r="D181" s="16"/>
+      <c r="E181" s="16"/>
+      <c r="F181" s="17"/>
+      <c r="G181" s="16"/>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" s="16"/>
+      <c r="B182" s="16"/>
+      <c r="C182" s="16"/>
+      <c r="D182" s="16"/>
+      <c r="E182" s="16"/>
+      <c r="F182" s="17"/>
+      <c r="G182" s="16"/>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" s="16"/>
+      <c r="B183" s="16"/>
+      <c r="C183" s="16"/>
+      <c r="D183" s="16"/>
+      <c r="E183" s="16"/>
+      <c r="F183" s="17"/>
+      <c r="G183" s="16"/>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" s="16"/>
+      <c r="B184" s="16"/>
+      <c r="C184" s="16"/>
+      <c r="D184" s="16"/>
+      <c r="E184" s="16"/>
+      <c r="F184" s="17"/>
+      <c r="G184" s="16"/>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" s="16"/>
+      <c r="B185" s="16"/>
+      <c r="C185" s="16"/>
+      <c r="D185" s="16"/>
+      <c r="E185" s="16"/>
+      <c r="F185" s="17"/>
+      <c r="G185" s="16"/>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" s="16"/>
+      <c r="B186" s="16"/>
+      <c r="C186" s="16"/>
+      <c r="D186" s="16"/>
+      <c r="E186" s="16"/>
+      <c r="F186" s="17"/>
+      <c r="G186" s="16"/>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" s="16"/>
+      <c r="B187" s="16"/>
+      <c r="C187" s="16"/>
+      <c r="D187" s="16"/>
+      <c r="E187" s="16"/>
+      <c r="F187" s="17"/>
+      <c r="G187" s="16"/>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" s="16"/>
+      <c r="B188" s="16"/>
+      <c r="C188" s="16"/>
+      <c r="D188" s="16"/>
+      <c r="E188" s="16"/>
+      <c r="F188" s="17"/>
+      <c r="G188" s="16"/>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189" s="16"/>
+      <c r="B189" s="16"/>
+      <c r="C189" s="16"/>
+      <c r="D189" s="16"/>
+      <c r="E189" s="16"/>
+      <c r="F189" s="17"/>
+      <c r="G189" s="16"/>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" s="16"/>
+      <c r="B190" s="16"/>
+      <c r="C190" s="16"/>
+      <c r="D190" s="16"/>
+      <c r="E190" s="16"/>
+      <c r="F190" s="17"/>
+      <c r="G190" s="16"/>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" s="16"/>
+      <c r="B191" s="16"/>
+      <c r="C191" s="16"/>
+      <c r="D191" s="16"/>
+      <c r="E191" s="16"/>
+      <c r="F191" s="17"/>
+      <c r="G191" s="16"/>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" s="16"/>
+      <c r="B192" s="16"/>
+      <c r="C192" s="16"/>
+      <c r="D192" s="16"/>
+      <c r="E192" s="16"/>
+      <c r="F192" s="17"/>
+      <c r="G192" s="16"/>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" s="16"/>
+      <c r="B193" s="16"/>
+      <c r="C193" s="16"/>
+      <c r="D193" s="16"/>
+      <c r="E193" s="16"/>
+      <c r="F193" s="17"/>
+      <c r="G193" s="16"/>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" s="16"/>
+      <c r="B194" s="16"/>
+      <c r="C194" s="16"/>
+      <c r="D194" s="16"/>
+      <c r="E194" s="16"/>
+      <c r="F194" s="17"/>
+      <c r="G194" s="16"/>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" s="16"/>
+      <c r="B195" s="16"/>
+      <c r="C195" s="16"/>
+      <c r="D195" s="16"/>
+      <c r="E195" s="16"/>
+      <c r="F195" s="17"/>
+      <c r="G195" s="16"/>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" s="16"/>
+      <c r="B196" s="16"/>
+      <c r="C196" s="16"/>
+      <c r="D196" s="16"/>
+      <c r="E196" s="16"/>
+      <c r="F196" s="17"/>
+      <c r="G196" s="16"/>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" s="16"/>
+      <c r="B197" s="16"/>
+      <c r="C197" s="16"/>
+      <c r="D197" s="16"/>
+      <c r="E197" s="16"/>
+      <c r="F197" s="17"/>
+      <c r="G197" s="16"/>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" s="16"/>
+      <c r="B198" s="16"/>
+      <c r="C198" s="16"/>
+      <c r="D198" s="16"/>
+      <c r="E198" s="16"/>
+      <c r="F198" s="17"/>
+      <c r="G198" s="16"/>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" s="16"/>
+      <c r="B199" s="16"/>
+      <c r="C199" s="16"/>
+      <c r="D199" s="16"/>
+      <c r="E199" s="16"/>
+      <c r="F199" s="17"/>
+      <c r="G199" s="16"/>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" s="16"/>
+      <c r="B200" s="16"/>
+      <c r="C200" s="16"/>
+      <c r="D200" s="16"/>
+      <c r="E200" s="16"/>
+      <c r="F200" s="17"/>
+      <c r="G200" s="16"/>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" s="16"/>
+      <c r="B201" s="16"/>
+      <c r="C201" s="16"/>
+      <c r="D201" s="16"/>
+      <c r="E201" s="16"/>
+      <c r="F201" s="17"/>
+      <c r="G201" s="16"/>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" s="16"/>
+      <c r="B202" s="16"/>
+      <c r="C202" s="16"/>
+      <c r="D202" s="16"/>
+      <c r="E202" s="16"/>
+      <c r="F202" s="17"/>
+      <c r="G202" s="16"/>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" s="16"/>
+      <c r="B203" s="16"/>
+      <c r="C203" s="16"/>
+      <c r="D203" s="16"/>
+      <c r="E203" s="16"/>
+      <c r="F203" s="17"/>
+      <c r="G203" s="16"/>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" s="16"/>
+      <c r="B204" s="16"/>
+      <c r="C204" s="16"/>
+      <c r="D204" s="16"/>
+      <c r="E204" s="16"/>
+      <c r="F204" s="17"/>
+      <c r="G204" s="16"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:F24" etc:filterBottomFollowUsedRange="0">
@@ -5096,7 +7318,7 @@
   </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -5121,7 +7343,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>290</v>
+        <v>336</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5129,10 +7351,10 @@
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
       <c r="G1" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:8">
@@ -5140,7 +7362,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>292</v>
+        <v>338</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>2</v>
@@ -5166,25 +7388,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>293</v>
+        <v>339</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>293</v>
+        <v>339</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>294</v>
+        <v>340</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>295</v>
+        <v>341</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:8">
@@ -5192,25 +7414,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>296</v>
+        <v>342</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>297</v>
+        <v>343</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>296</v>
+        <v>342</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8">
@@ -5218,25 +7440,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>299</v>
+        <v>345</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>300</v>
+        <v>346</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>301</v>
+        <v>347</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>302</v>
+        <v>348</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:8">
@@ -5244,25 +7466,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>303</v>
+        <v>349</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8">
@@ -5270,25 +7492,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>305</v>
+        <v>351</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8">
@@ -5296,25 +7518,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>307</v>
+        <v>353</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>308</v>
+        <v>354</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>302</v>
+        <v>348</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:8">
@@ -5322,25 +7544,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>309</v>
+        <v>355</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:8">
@@ -5348,25 +7570,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>312</v>
+        <v>358</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8">
@@ -5374,25 +7596,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>313</v>
+        <v>359</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>314</v>
+        <v>360</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>315</v>
+        <v>361</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>316</v>
+        <v>362</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>317</v>
+        <v>363</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:8">
@@ -5400,25 +7622,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>318</v>
+        <v>364</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>319</v>
+        <v>365</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>320</v>
+        <v>366</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:8">
@@ -5426,25 +7648,25 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>321</v>
+        <v>367</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>322</v>
+        <v>368</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>320</v>
+        <v>366</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:8">
@@ -5452,25 +7674,25 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>323</v>
+        <v>369</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>325</v>
+        <v>371</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:8">
@@ -5478,25 +7700,25 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>326</v>
+        <v>372</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>327</v>
+        <v>373</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>328</v>
+        <v>374</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:8">
@@ -5504,25 +7726,25 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>330</v>
+        <v>376</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>320</v>
+        <v>366</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:8">
@@ -5530,25 +7752,25 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>331</v>
+        <v>377</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>332</v>
+        <v>378</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>333</v>
+        <v>379</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:8">
@@ -5556,25 +7778,25 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>334</v>
+        <v>380</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>335</v>
+        <v>381</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8">
@@ -5582,25 +7804,25 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:8">
@@ -5608,25 +7830,25 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>339</v>
+        <v>385</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>317</v>
+        <v>363</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:8">
@@ -5634,25 +7856,25 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>342</v>
+        <v>388</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>343</v>
+        <v>389</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>317</v>
+        <v>363</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:8">
@@ -5660,25 +7882,25 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>344</v>
+        <v>390</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>345</v>
+        <v>391</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>346</v>
+        <v>392</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>317</v>
+        <v>363</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:8">
@@ -5686,13 +7908,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>348</v>
+        <v>394</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>17</v>
@@ -5701,10 +7923,10 @@
         <v>34</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:8">
@@ -5712,25 +7934,25 @@
         <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>350</v>
+        <v>396</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>351</v>
+        <v>397</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>317</v>
+        <v>363</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:8">
@@ -5738,25 +7960,25 @@
         <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>352</v>
+        <v>398</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>353</v>
+        <v>399</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>317</v>
+        <v>363</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:8">
@@ -5764,13 +7986,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>355</v>
+        <v>401</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>17</v>
@@ -5779,10 +8001,10 @@
         <v>69</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:8">
@@ -5790,25 +8012,25 @@
         <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>356</v>
+        <v>402</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>357</v>
+        <v>403</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>317</v>
+        <v>363</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -5841,7 +8063,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>404</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5849,10 +8071,10 @@
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
       <c r="G1" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:8">
@@ -5860,7 +8082,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>292</v>
+        <v>338</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>2</v>
@@ -5886,25 +8108,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>293</v>
+        <v>339</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>293</v>
+        <v>339</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>294</v>
+        <v>340</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>295</v>
+        <v>341</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:8">
@@ -5912,25 +8134,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>296</v>
+        <v>342</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>297</v>
+        <v>343</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>296</v>
+        <v>342</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8">
@@ -5938,25 +8160,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>299</v>
+        <v>345</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>359</v>
+        <v>405</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>360</v>
+        <v>406</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>302</v>
+        <v>348</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:8">
@@ -5964,25 +8186,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>361</v>
+        <v>407</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>362</v>
+        <v>408</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8">
@@ -5990,25 +8212,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>363</v>
+        <v>409</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>364</v>
+        <v>410</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8">
@@ -6016,25 +8238,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>365</v>
+        <v>411</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>366</v>
+        <v>412</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>367</v>
+        <v>413</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:8">
@@ -6042,25 +8264,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>368</v>
+        <v>414</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>369</v>
+        <v>415</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>370</v>
+        <v>416</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:8">
@@ -6068,25 +8290,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>371</v>
+        <v>417</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>372</v>
+        <v>418</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>367</v>
+        <v>413</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8">
@@ -6094,25 +8316,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>373</v>
+        <v>419</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>374</v>
+        <v>420</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -6144,7 +8366,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>421</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6181,16 +8403,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>376</v>
+        <v>422</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>377</v>
+        <v>423</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>378</v>
+        <v>424</v>
       </c>
       <c r="F3" s="6">
         <v>1.2</v>
@@ -6202,16 +8424,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>379</v>
+        <v>425</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>380</v>
+        <v>426</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>381</v>
+        <v>427</v>
       </c>
       <c r="F4" s="6">
         <v>0.8</v>
@@ -6223,16 +8445,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>382</v>
+        <v>428</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>383</v>
+        <v>429</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>384</v>
+        <v>430</v>
       </c>
       <c r="F5" s="6">
         <v>0.5</v>
@@ -6244,16 +8466,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>385</v>
+        <v>431</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>386</v>
+        <v>432</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F6" s="6">
         <v>0.5</v>
@@ -6265,16 +8487,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>387</v>
+        <v>433</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>388</v>
+        <v>434</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>381</v>
+        <v>427</v>
       </c>
       <c r="F7" s="6">
         <v>0.5</v>
@@ -6283,7 +8505,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>389</v>
+        <v>435</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -6320,16 +8542,16 @@
         <v>1</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>376</v>
+        <v>422</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>377</v>
+        <v>423</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>390</v>
+        <v>436</v>
       </c>
       <c r="F10" s="6">
         <v>1.2</v>
@@ -6341,16 +8563,16 @@
         <v>2</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>379</v>
+        <v>425</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>380</v>
+        <v>426</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>381</v>
+        <v>427</v>
       </c>
       <c r="F11" s="6">
         <v>0.8</v>
@@ -6362,16 +8584,16 @@
         <v>3</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>382</v>
+        <v>428</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>383</v>
+        <v>429</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>384</v>
+        <v>430</v>
       </c>
       <c r="F12" s="6">
         <v>0.5</v>
@@ -6383,16 +8605,16 @@
         <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>385</v>
+        <v>431</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>386</v>
+        <v>432</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F13" s="6">
         <v>0.5</v>
@@ -6404,16 +8626,16 @@
         <v>5</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>391</v>
+        <v>437</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>388</v>
+        <v>434</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>381</v>
+        <v>427</v>
       </c>
       <c r="F14" s="6">
         <v>0.5</v>
@@ -6425,16 +8647,16 @@
         <v>6</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>392</v>
+        <v>438</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>393</v>
+        <v>439</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F15" s="6">
         <v>0.5</v>
@@ -6446,16 +8668,16 @@
         <v>7</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>394</v>
+        <v>440</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>395</v>
+        <v>441</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F16" s="6">
         <v>0.5</v>
@@ -6467,16 +8689,16 @@
         <v>8</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>397</v>
+        <v>443</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>398</v>
+        <v>444</v>
       </c>
       <c r="F17" s="6">
         <v>0.5</v>
@@ -6488,16 +8710,16 @@
         <v>9</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>399</v>
+        <v>445</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>400</v>
+        <v>446</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>401</v>
+        <v>447</v>
       </c>
       <c r="F18" s="6">
         <v>0.4</v>
@@ -6509,16 +8731,16 @@
         <v>10</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>402</v>
+        <v>448</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>403</v>
+        <v>449</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="F19" s="6">
         <v>0.1</v>

--- a/hypermesh/仿真建模规范-手机.xlsx
+++ b/hypermesh/仿真建模规范-手机.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="4"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="1-主板建模规范" sheetId="1" r:id="rId1"/>
@@ -175,7 +175,7 @@
     <t>P_SENSOR_DIANGAOAOBAN</t>
   </si>
   <si>
-    <t>压力传感器垫高板</t>
+    <t>光感垫高板</t>
   </si>
   <si>
     <t>/</t>
@@ -184,13 +184,13 @@
     <t>P_SENSOR_DIANGAOAOBAN_SOLDER</t>
   </si>
   <si>
-    <t>压力传感器垫高板焊锡</t>
+    <t>光感垫高板焊锡</t>
   </si>
   <si>
     <t>P_SENSOR_SOLDER</t>
   </si>
   <si>
-    <t>压力传感器焊锡</t>
+    <t>光感焊锡</t>
   </si>
   <si>
     <t>P_SENSOR</t>

--- a/hypermesh/仿真建模规范-手机.xlsx
+++ b/hypermesh/仿真建模规范-手机.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="1-主板建模规范" sheetId="1" r:id="rId1"/>
@@ -4733,9 +4733,6 @@
       <c r="D28" s="18"/>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
-      <c r="G28" s="5" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:7">
       <c r="A29" s="10" t="s">
@@ -4756,7 +4753,9 @@
       <c r="F29" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="7"/>
+      <c r="G29" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:7">
       <c r="A30" s="21">
